--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/CALIFORNIA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/CALIFORNIA_2023.xlsx
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C263">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C432">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Huehuetl</t>
+          <t>Huehuetla</t>
         </is>
       </c>
       <c r="C577">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C580">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>Santa Ana Tlapacoya</t>
+          <t>Santa Ana Tlapacoyan</t>
         </is>
       </c>
       <c r="C1301">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1456">
@@ -33900,7 +33900,7 @@
       </c>
       <c r="B1864" t="inlineStr">
         <is>
-          <t>San Pedro De La Cuev</t>
+          <t>San Pedro De La Cueva</t>
         </is>
       </c>
       <c r="C1864">
@@ -35898,7 +35898,7 @@
       </c>
       <c r="B1975" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1975">
